--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58067</v>
+        <v>58122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>98644628</v>
       </c>
       <c r="B9" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,51 +1323,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64785892</v>
+        <v>137451926</v>
       </c>
       <c r="B8" t="n">
-        <v>92567</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562374</v>
+        <v>562354</v>
       </c>
       <c r="R8" t="n">
-        <v>6465165</v>
+        <v>6465148</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-12-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-12-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,58 +1423,60 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64785892</t>
+          <t>https://artportalen.se/Sighting/137451926</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98644628</v>
+        <v>64785892</v>
       </c>
       <c r="B9" t="n">
-        <v>58149</v>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100090</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562354</v>
+        <v>562374</v>
       </c>
       <c r="R9" t="n">
-        <v>6465187</v>
+        <v>6465165</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,17 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2016-12-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Nötkråkor har egentligen observerats regelbunden i området under de senaste 6 åren och särskilt på vintern. Längre in i skogsområdet finns det en s.k. fröplantering av vitgran i åldersklassen 10 till 20 år som ursakats av nötkråkan när den inte hittad igen sina gömda frön vilket bevisar en närvaro av nötkråkor under åtminstone 20 år i området!</t>
+          <t>2016-12-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,6 +1514,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,56 +1532,44 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98644628</t>
+          <t>https://artportalen.se/Sighting/64785892</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700365</v>
+        <v>98644628</v>
       </c>
       <c r="B10" t="n">
-        <v>57947</v>
+        <v>58149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>100090</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1594,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562375</v>
+        <v>562354</v>
       </c>
       <c r="R10" t="n">
-        <v>6465184</v>
+        <v>6465187</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,12 +1607,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Nötkråkor har egentligen observerats regelbunden i området under de senaste 6 åren och särskilt på vintern. Längre in i skogsområdet finns det en s.k. fröplantering av vitgran i åldersklassen 10 till 20 år som ursakats av nötkråkan när den inte hittad igen sina gömda frön vilket bevisar en närvaro av nötkråkor under åtminstone 20 år i området!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,65 +1643,70 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122700365</t>
+          <t>https://artportalen.se/Sighting/98644628</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100162576</v>
+        <v>122700365</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>57947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtvidaberg, Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562366</v>
+        <v>562375</v>
       </c>
       <c r="R11" t="n">
-        <v>6465125</v>
+        <v>6465184</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,12 +1730,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,24 +1750,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100162576</t>
+          <t>https://artportalen.se/Sighting/122700365</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110106837</v>
+        <v>100162576</v>
       </c>
       <c r="B12" t="n">
         <v>58114</v>
@@ -1802,24 +1795,31 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Åtvidaberg, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562336</v>
+        <v>562366</v>
       </c>
       <c r="R12" t="n">
-        <v>6465130</v>
+        <v>6465125</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,17 +1843,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>i häckningsrevir</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,59 +1863,55 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110106837</t>
+          <t>https://artportalen.se/Sighting/100162576</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93065983</v>
+        <v>110106837</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1928,13 +1919,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562369</v>
+        <v>562336</v>
       </c>
       <c r="R13" t="n">
-        <v>6465186</v>
+        <v>6465130</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,12 +1949,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>i häckningsrevir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1968,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,13 +1985,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93065983</t>
+          <t>https://artportalen.se/Sighting/110106837</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110267630</v>
+        <v>93065983</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2026,7 +2021,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2039,13 +2034,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562372</v>
+        <v>562369</v>
       </c>
       <c r="R14" t="n">
-        <v>6465193</v>
+        <v>6465186</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,12 +2064,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,13 +2096,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110267630</t>
+          <t>https://artportalen.se/Sighting/93065983</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110267644</v>
+        <v>110267630</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2137,7 +2132,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2150,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562345</v>
+        <v>562372</v>
       </c>
       <c r="R15" t="n">
-        <v>6465188</v>
+        <v>6465193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,13 +2207,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110267644</t>
+          <t>https://artportalen.se/Sighting/110267630</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111357197</v>
+        <v>110267644</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2261,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562360</v>
+        <v>562345</v>
       </c>
       <c r="R16" t="n">
-        <v>6465140</v>
+        <v>6465188</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2286,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,13 +2318,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111357197</t>
+          <t>https://artportalen.se/Sighting/110267644</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129732505</v>
+        <v>111357197</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2359,7 +2354,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2368,17 +2363,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Byrum, Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562358</v>
+        <v>562360</v>
       </c>
       <c r="R17" t="n">
-        <v>6465194</v>
+        <v>6465140</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,12 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,49 +2418,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129732505</t>
+          <t>https://artportalen.se/Sighting/111357197</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96256837</v>
+        <v>129732505</v>
       </c>
       <c r="B18" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2479,17 +2474,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Byrum, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562409</v>
+        <v>562358</v>
       </c>
       <c r="R18" t="n">
-        <v>6465154</v>
+        <v>6465194</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2513,12 +2508,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,27 +2529,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96256837</t>
+          <t>https://artportalen.se/Sighting/129732505</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96970532</v>
+        <v>96256837</v>
       </c>
       <c r="B19" t="n">
-        <v>106231</v>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,24 +2557,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224098</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -2590,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562326</v>
+        <v>562409</v>
       </c>
       <c r="R19" t="n">
-        <v>6465155</v>
+        <v>6465154</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2620,12 +2619,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,6 +2650,113 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96256837</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96970532</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>562326</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6465155</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96970532</t>
         </is>
@@ -2676,6 +2782,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>137451926</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
